--- a/GEMINI/Files/TEMPLATE_BUP_WSO.xlsx
+++ b/GEMINI/Files/TEMPLATE_BUP_WSO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\@Tasks\#FILES\MERSY\Upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_tp\wSo\GEMINI\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37DC4C27-E59E-4E66-B161-1C43E73ED4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D24CC99-A362-4105-A910-E4D6E5C43F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{71F8C813-B4ED-4C53-B0D6-BE95CDFF7AF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{71F8C813-B4ED-4C53-B0D6-BE95CDFF7AF2}"/>
   </bookViews>
   <sheets>
     <sheet name="WSO" sheetId="1" r:id="rId1"/>
@@ -310,7 +310,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,8 +340,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,6 +366,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -382,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -404,11 +425,29 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -801,13 +840,13 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -819,16 +858,16 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
@@ -837,7 +876,7 @@
       <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="12" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="3" t="s">
@@ -870,19 +909,19 @@
       <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -933,13 +972,13 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -951,16 +990,16 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
@@ -969,7 +1008,7 @@
       <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="12" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="3" t="s">
@@ -1002,13 +1041,13 @@
       <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
